--- a/outputs/Validation_Report.xlsx
+++ b/outputs/Validation_Report.xlsx
@@ -2479,7 +2479,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-17 12:31:43</t>
+          <t>2026-06-18 01:53:19</t>
         </is>
       </c>
     </row>
